--- a/output/pdf_financials_xlsx/DWTZ.xlsx
+++ b/output/pdf_financials_xlsx/DWTZ.xlsx
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.838123</v>
+        <v>0.836761</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.352115</v>
+        <v>0.35</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -5592,7 +5592,11 @@
           <t>Exploration and evaluation expenditures 6</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -6248,7 +6252,11 @@
           <t>Exploration and evaluation expenditures 8</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>-0.001362</v>
       </c>

--- a/output/pdf_financials_xlsx/DWTZ.xlsx
+++ b/output/pdf_financials_xlsx/DWTZ.xlsx
@@ -1086,7 +1086,7 @@
         <v>0.142444</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000102</v>
       </c>
     </row>
     <row r="35">
@@ -1124,7 +1124,7 @@
         <v>0.142444</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000102</v>
       </c>
     </row>
     <row r="37">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3176,7 +3176,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>-</t>
@@ -3648,7 +3652,11 @@
           <t>Reclamation deposits 2</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>0.06</v>
       </c>
@@ -6608,7 +6616,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -7446,7 +7454,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">

--- a/output/pdf_financials_xlsx/DWTZ.xlsx
+++ b/output/pdf_financials_xlsx/DWTZ.xlsx
@@ -547,10 +547,10 @@
         <v>0.165317</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.154365</v>
+        <v>0.156365</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.122517</v>
+        <v>0.137517</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>2.005541</v>
@@ -6510,7 +6510,11 @@
           <t>Director fees 8</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -7380,7 +7384,11 @@
           <t>Director fees 9</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -8142,7 +8150,11 @@
           <t>Director fees</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
